--- a/Year_0.xlsx
+++ b/Year_0.xlsx
@@ -10,21 +10,25 @@
     <sheet name="NO_Variable_Pool_Number" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="NO_Variable_Recruitment_Amount" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="NO_Variable_Depth_cm" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="pNO_Variable_Julian_Day" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="pNO_Variable_Pool_Number" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="pNO_Variable_Recruitment_Amount" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="pNO_Variable_Depth_cm" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Ests_Overall" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Ests_Overall_sd" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="overall_pvalues" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="separate_values" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="overall_clusdiff_pvalues" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="NO_Variable_Temp_Reg" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="NO_Variable_O2_Reg" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="pNO_Variable_Julian_Day" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="pNO_Variable_Pool_Number" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="pNO_Variable_Recruitment_Amount" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="pNO_Variable_Depth_cm" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="pNO_Variable_Temp_Reg" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="pNO_Variable_O2_Reg" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Ests_Overall" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Ests_Overall_sd" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="overall_pvalues" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="separate_clus_diff_pvalues" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="overall_clusdiff_pvalues" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -56,6 +60,9 @@
     <t xml:space="preserve">Springtail</t>
   </si>
   <si>
+    <t xml:space="preserve">varname</t>
+  </si>
+  <si>
     <t xml:space="preserve">separate.cluster.pvalues</t>
   </si>
   <si>
@@ -65,13 +72,37 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
+    <t xml:space="preserve">Julian_Day</t>
+  </si>
+  <si>
     <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pool_Number</t>
   </si>
   <si>
     <t xml:space="preserve">3</t>
   </si>
   <si>
+    <t xml:space="preserve">Recruitment_Amount</t>
+  </si>
+  <si>
     <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depth_cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temp_Reg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O2_Reg</t>
   </si>
   <si>
     <t xml:space="preserve">overall.cluster.pvalues</t>
@@ -445,282 +476,250 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.201655487327661</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.172991360903324</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.228047891171238</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.235232465363457</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.198977146551827</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.533408615312995</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.559642997355224</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.125972553451966</v>
-      </c>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
-        <v>0.201655487327661</v>
-      </c>
+      <c r="B3"/>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.583064454851921</v>
+        <v>0.528577532852903</v>
       </c>
       <c r="E3" t="n">
-        <v>0.734248917562526</v>
+        <v>0.701910191615105</v>
       </c>
       <c r="F3" t="n">
-        <v>0.416069793345463</v>
+        <v>0.327721648151118</v>
       </c>
       <c r="G3" t="n">
-        <v>0.724053156711722</v>
+        <v>0.840571915510596</v>
       </c>
       <c r="H3" t="n">
-        <v>0.19888277736834</v>
+        <v>0.215909831721117</v>
       </c>
       <c r="I3" t="n">
-        <v>0.435646243972267</v>
+        <v>0.709276902022228</v>
       </c>
       <c r="J3" t="n">
-        <v>0.113143361174873</v>
+        <v>0.262883506671075</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
-        <v>0.172991360903324</v>
-      </c>
+      <c r="B4"/>
       <c r="C4" t="n">
-        <v>0.583064454851921</v>
+        <v>0.528577532852903</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.716819760987004</v>
+        <v>0.695610558414576</v>
       </c>
       <c r="F4" t="n">
-        <v>0.674242066064819</v>
+        <v>0.72338558727488</v>
       </c>
       <c r="G4" t="n">
-        <v>0.723597482780387</v>
+        <v>0.634160771424536</v>
       </c>
       <c r="H4" t="n">
-        <v>0.144879225729122</v>
+        <v>0.229676205769271</v>
       </c>
       <c r="I4" t="n">
-        <v>0.42745232945141</v>
+        <v>0.655614101367303</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0372170630451972</v>
+        <v>0.302829888039673</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
-        <v>0.228047891171238</v>
-      </c>
+      <c r="B5"/>
       <c r="C5" t="n">
-        <v>0.734248917562526</v>
+        <v>0.701910191615105</v>
       </c>
       <c r="D5" t="n">
-        <v>0.716819760987004</v>
+        <v>0.695610558414576</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.444089188142604</v>
+        <v>0.507957191246881</v>
       </c>
       <c r="G5" t="n">
-        <v>0.710624118911074</v>
+        <v>0.621987891500617</v>
       </c>
       <c r="H5" t="n">
-        <v>0.25193411657478</v>
+        <v>0.317341684710991</v>
       </c>
       <c r="I5" t="n">
-        <v>0.512052770598514</v>
+        <v>0.814421110231895</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0626283791158904</v>
+        <v>0.396304740717911</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
-        <v>0.235232465363457</v>
-      </c>
+      <c r="B6"/>
       <c r="C6" t="n">
-        <v>0.416069793345463</v>
+        <v>0.327721648151118</v>
       </c>
       <c r="D6" t="n">
-        <v>0.674242066064819</v>
+        <v>0.72338558727488</v>
       </c>
       <c r="E6" t="n">
-        <v>0.444089188142604</v>
+        <v>0.507957191246881</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.424552003750586</v>
+        <v>0.422644520811489</v>
       </c>
       <c r="H6" t="n">
-        <v>0.269446239578976</v>
+        <v>0.326999261878618</v>
       </c>
       <c r="I6" t="n">
-        <v>0.461501945752968</v>
+        <v>0.415980398984572</v>
       </c>
       <c r="J6" t="n">
-        <v>0.181106746106641</v>
+        <v>0.403354360888331</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
-        <v>0.198977146551827</v>
-      </c>
+      <c r="B7"/>
       <c r="C7" t="n">
-        <v>0.724053156711722</v>
+        <v>0.840571915510596</v>
       </c>
       <c r="D7" t="n">
-        <v>0.723597482780387</v>
+        <v>0.634160771424536</v>
       </c>
       <c r="E7" t="n">
-        <v>0.710624118911074</v>
+        <v>0.621987891500617</v>
       </c>
       <c r="F7" t="n">
-        <v>0.424552003750586</v>
+        <v>0.422644520811489</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.136295799624729</v>
+        <v>0.15530375391399</v>
       </c>
       <c r="I7" t="n">
-        <v>0.440692864538082</v>
+        <v>0.6462194884632</v>
       </c>
       <c r="J7" t="n">
-        <v>0.025007349114115</v>
+        <v>0.196430709914822</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
-        <v>0.533408615312995</v>
-      </c>
+      <c r="B8"/>
       <c r="C8" t="n">
-        <v>0.19888277736834</v>
+        <v>0.215909831721117</v>
       </c>
       <c r="D8" t="n">
-        <v>0.144879225729122</v>
+        <v>0.229676205769271</v>
       </c>
       <c r="E8" t="n">
-        <v>0.25193411657478</v>
+        <v>0.317341684710991</v>
       </c>
       <c r="F8" t="n">
-        <v>0.269446239578976</v>
+        <v>0.326999261878618</v>
       </c>
       <c r="G8" t="n">
-        <v>0.136295799624729</v>
+        <v>0.15530375391399</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.449745102367975</v>
+        <v>0.236087596677075</v>
       </c>
       <c r="J8" t="n">
-        <v>0.311321489735757</v>
+        <v>0.566624605562677</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
-        <v>0.559642997355224</v>
-      </c>
+      <c r="B9"/>
       <c r="C9" t="n">
-        <v>0.435646243972267</v>
+        <v>0.709276902022228</v>
       </c>
       <c r="D9" t="n">
-        <v>0.42745232945141</v>
+        <v>0.655614101367303</v>
       </c>
       <c r="E9" t="n">
-        <v>0.512052770598514</v>
+        <v>0.814421110231895</v>
       </c>
       <c r="F9" t="n">
-        <v>0.461501945752968</v>
+        <v>0.415980398984572</v>
       </c>
       <c r="G9" t="n">
-        <v>0.440692864538082</v>
+        <v>0.6462194884632</v>
       </c>
       <c r="H9" t="n">
-        <v>0.449745102367975</v>
+        <v>0.236087596677075</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.117208621798812</v>
+        <v>0.308366671746014</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
-        <v>0.125972553451966</v>
-      </c>
+      <c r="B10"/>
       <c r="C10" t="n">
-        <v>0.113143361174873</v>
+        <v>0.262883506671075</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0372170630451972</v>
+        <v>0.302829888039673</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0626283791158904</v>
+        <v>0.396304740717911</v>
       </c>
       <c r="F10" t="n">
-        <v>0.181106746106641</v>
+        <v>0.403354360888331</v>
       </c>
       <c r="G10" t="n">
-        <v>0.025007349114115</v>
+        <v>0.196430709914822</v>
       </c>
       <c r="H10" t="n">
-        <v>0.311321489735757</v>
+        <v>0.566624605562677</v>
       </c>
       <c r="I10" t="n">
-        <v>0.117208621798812</v>
+        <v>0.308366671746014</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -774,287 +773,255 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.0500067124501191</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.125608368521044</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.175936630377433</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.149412962330443</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.0757166332609094</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.10378790153505</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.193640961439475</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.180751294414136</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
-        <v>0.0500067124501191</v>
-      </c>
+      <c r="B3"/>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.18788638070484</v>
+        <v>0.052</v>
       </c>
       <c r="E3" t="n">
-        <v>0.111773725908482</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.235452323334348</v>
+        <v>0.216</v>
       </c>
       <c r="G3" t="n">
-        <v>0.170784987434198</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0493719842925594</v>
+        <v>0.22</v>
       </c>
       <c r="I3" t="n">
-        <v>0.110437114031658</v>
+        <v>0.029</v>
       </c>
       <c r="J3" t="n">
-        <v>0.159965209857613</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
-        <v>0.125608368521044</v>
-      </c>
+      <c r="B4"/>
       <c r="C4" t="n">
-        <v>0.18788638070484</v>
+        <v>0.052</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0802347020786892</v>
+        <v>0.008</v>
       </c>
       <c r="F4" t="n">
-        <v>0.333809390209184</v>
+        <v>0.495</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0842399658660999</v>
+        <v>0.884</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0375903786499739</v>
+        <v>0.214</v>
       </c>
       <c r="I4" t="n">
-        <v>0.050312873223844</v>
+        <v>0.075</v>
       </c>
       <c r="J4" t="n">
-        <v>0.18116234635752</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
-        <v>0.175936630377433</v>
-      </c>
+      <c r="B5"/>
       <c r="C5" t="n">
-        <v>0.111773725908482</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0802347020786892</v>
+        <v>0.008</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.132334775261016</v>
+        <v>0.036</v>
       </c>
       <c r="G5" t="n">
-        <v>0.105639517472836</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.11482936470157</v>
+        <v>0.07</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0928288332071178</v>
+        <v>0.712</v>
       </c>
       <c r="J5" t="n">
-        <v>0.228933400108505</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
-        <v>0.149412962330443</v>
-      </c>
+      <c r="B6"/>
       <c r="C6" t="n">
-        <v>0.235452323334348</v>
+        <v>0.216</v>
       </c>
       <c r="D6" t="n">
-        <v>0.333809390209184</v>
+        <v>0.495</v>
       </c>
       <c r="E6" t="n">
-        <v>0.132334775261016</v>
+        <v>0.036</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.202322725415112</v>
+        <v>0.167</v>
       </c>
       <c r="H6" t="n">
-        <v>0.28498867796663</v>
+        <v>0.265</v>
       </c>
       <c r="I6" t="n">
-        <v>0.055042333668149</v>
+        <v>0.13</v>
       </c>
       <c r="J6" t="n">
-        <v>0.102882260570565</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
-        <v>0.0757166332609094</v>
-      </c>
+      <c r="B7"/>
       <c r="C7" t="n">
-        <v>0.170784987434198</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0842399658660999</v>
+        <v>0.884</v>
       </c>
       <c r="E7" t="n">
-        <v>0.105639517472836</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.202322725415112</v>
+        <v>0.167</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.043604949106812</v>
+        <v>0.073</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0291914606185107</v>
+        <v>0.006</v>
       </c>
       <c r="J7" t="n">
-        <v>0.244488341235076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
-        <v>0.10378790153505</v>
-      </c>
+      <c r="B8"/>
       <c r="C8" t="n">
-        <v>0.0493719842925594</v>
+        <v>0.22</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0375903786499739</v>
+        <v>0.214</v>
       </c>
       <c r="E8" t="n">
-        <v>0.11482936470157</v>
+        <v>0.07</v>
       </c>
       <c r="F8" t="n">
-        <v>0.28498867796663</v>
+        <v>0.265</v>
       </c>
       <c r="G8" t="n">
-        <v>0.043604949106812</v>
+        <v>0.073</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.117290251198048</v>
+        <v>0.147</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0977725864808763</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
-        <v>0.193640961439475</v>
-      </c>
+      <c r="B9"/>
       <c r="C9" t="n">
-        <v>0.110437114031658</v>
+        <v>0.029</v>
       </c>
       <c r="D9" t="n">
-        <v>0.050312873223844</v>
+        <v>0.075</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0928288332071178</v>
+        <v>0.712</v>
       </c>
       <c r="F9" t="n">
-        <v>0.055042333668149</v>
+        <v>0.13</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0291914606185107</v>
+        <v>0.006</v>
       </c>
       <c r="H9" t="n">
-        <v>0.117290251198048</v>
+        <v>0.147</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.260924873724725</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
-        <v>0.180751294414136</v>
-      </c>
+      <c r="B10"/>
       <c r="C10" t="n">
-        <v>0.159965209857613</v>
+        <v>0.002</v>
       </c>
       <c r="D10" t="n">
-        <v>0.18116234635752</v>
+        <v>0.001</v>
       </c>
       <c r="E10" t="n">
-        <v>0.228933400108505</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.102882260570565</v>
+        <v>0.016</v>
       </c>
       <c r="G10" t="n">
-        <v>0.244488341235076</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0977725864808763</v>
+        <v>0.22</v>
       </c>
       <c r="I10" t="n">
-        <v>0.260924873724725</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1107,38 +1074,20 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B3"/>
       <c r="C3" t="n">
         <v>1</v>
       </c>
@@ -1155,10 +1104,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.298</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -1168,9 +1117,7 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
+      <c r="B4"/>
       <c r="C4" t="n">
         <v>0</v>
       </c>
@@ -1178,19 +1125,19 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.545</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -1200,29 +1147,27 @@
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
+      <c r="B5"/>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.424</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009</v>
+        <v>0.1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1232,17 +1177,15 @@
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B6"/>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -1251,27 +1194,25 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.181</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
+      <c r="B7"/>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1283,10 +1224,10 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.428</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1296,58 +1237,54 @@
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
-        <v>0.016</v>
-      </c>
+      <c r="B8"/>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.298</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.545</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.424</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.181</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.428</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.188</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
+      <c r="B9"/>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009</v>
+        <v>0.1</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.188</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -1360,9 +1297,7 @@
       <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
+      <c r="B10"/>
       <c r="C10" t="n">
         <v>0</v>
       </c>
@@ -1373,13 +1308,13 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1404,53 +1339,286 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>11</v>
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0.013</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B3"/>
       <c r="C3" t="n">
-        <v>0.987</v>
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.036</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0.009</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B4"/>
       <c r="C4" t="n">
-        <v>0.991</v>
+        <v>0.001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.037</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B5"/>
       <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.568</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.043</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6"/>
+      <c r="C6" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.087</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.067</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7"/>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.029</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8"/>
+      <c r="C8" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.127</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9"/>
+      <c r="C9" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.568</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.087</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.109</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10"/>
+      <c r="C10" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="J10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1470,22 +1638,1000 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3"/>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.537173072902295</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.55336240513561</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.336863417038964</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.726463318854106</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.261046644485161</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.45625571547967</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.274900496916614</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4"/>
+      <c r="C4" t="n">
+        <v>0.537173072902295</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.569260681299747</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.498112567297203</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.598614273514517</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.271704587944988</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.478946731577935</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.258018031276504</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5"/>
+      <c r="C5" t="n">
+        <v>0.55336240513561</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.569260681299747</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.470235964331222</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.583106099103249</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.361552961112058</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.774292605334225</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.342598051042905</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6"/>
+      <c r="C6" t="n">
+        <v>0.336863417038964</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.498112567297203</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.470235964331222</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.364868825474739</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.318817344171886</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.431697367915212</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.417550652906001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7"/>
+      <c r="C7" t="n">
+        <v>0.726463318854106</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.598614273514517</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.583106099103249</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.364868825474739</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.232174041536287</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.503571615280837</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.21962645290931</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8"/>
+      <c r="C8" t="n">
+        <v>0.261046644485161</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.271704587944988</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.361552961112058</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.318817344171886</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.232174041536287</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.307235507647296</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.412051973910559</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9"/>
+      <c r="C9" t="n">
+        <v>0.45625571547967</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.478946731577935</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.774292605334225</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.431697367915212</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.503571615280837</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.307235507647296</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.298986405134172</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10"/>
+      <c r="C10" t="n">
+        <v>0.274900496916614</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.258018031276504</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.342598051042905</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.417550652906001</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.21962645290931</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.412051973910559</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.298986405134172</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3"/>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.134320896851475</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.173577054993552</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.208721240361544</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.147301336955862</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.126456940847549</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.217973576300817</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.147279813373123</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4"/>
+      <c r="C4" t="n">
+        <v>0.134320896851475</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.122071646809063</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.279273271566744</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.192031499730891</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.209360808852155</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0996009424278263</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.0627676553679778</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5"/>
+      <c r="C5" t="n">
+        <v>0.173577054993552</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.122071646809063</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.0923655696226465</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.109457765387933</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.21724371575638</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.0528919974205167</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.182150509063202</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6"/>
+      <c r="C6" t="n">
+        <v>0.208721240361544</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.279273271566744</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0923655696226465</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.211656507573077</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.139666822122181</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.0520631608726696</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.0609682028100487</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7"/>
+      <c r="C7" t="n">
+        <v>0.147301336955862</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.192031499730891</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.109457765387933</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.211656507573077</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.169717190740286</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.114866031553342</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.0917986649916031</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8"/>
+      <c r="C8" t="n">
+        <v>0.126456940847549</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.209360808852155</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.21724371575638</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.139666822122181</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.169717190740286</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.200215234354064</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.255828208290737</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9"/>
+      <c r="C9" t="n">
+        <v>0.217973576300817</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0996009424278263</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0528919974205167</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0520631608726696</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.114866031553342</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.200215234354064</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.20584743179722</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10"/>
+      <c r="C10" t="n">
+        <v>0.147279813373123</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.0627676553679778</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.182150509063202</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.0609682028100487</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.0917986649916031</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.255828208290737</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.20584743179722</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3"/>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4"/>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5"/>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6"/>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7"/>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8"/>
+      <c r="C8" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.289</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9"/>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10"/>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2"/>
+      <c r="D2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4"/>
+      <c r="D4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5"/>
+      <c r="D5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6"/>
+      <c r="D6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7"/>
+      <c r="D7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1537,282 +2683,282 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.205136813832466</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.167247386759582</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.317857142857143</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.585714285714286</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.179655455291222</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.752380952380952</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.23956043956044</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.123348694316436</v>
+      <c r="C2" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="D2" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="E2" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F2" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="G2" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="H2" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="I2" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="J2" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
-        <v>0.205136813832466</v>
+      <c r="B3" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.368777048522542</v>
+        <v>0.356536502546689</v>
       </c>
       <c r="E3" t="n">
-        <v>0.505896424374685</v>
+        <v>0.325698813764329</v>
       </c>
       <c r="F3" t="n">
-        <v>0.205966836401619</v>
+        <v>0.212676853423882</v>
       </c>
       <c r="G3" t="n">
-        <v>0.436445469259251</v>
+        <v>0.43985967413633</v>
       </c>
       <c r="H3" t="n">
-        <v>0.266118292205249</v>
+        <v>0.0899830220713073</v>
       </c>
       <c r="I3" t="n">
-        <v>0.224984181505921</v>
+        <v>0.147707979626486</v>
       </c>
       <c r="J3" t="n">
-        <v>0.205825741590117</v>
+        <v>0.344312393887946</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
-        <v>0.167247386759582</v>
+      <c r="B4" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="C4" t="n">
-        <v>0.368777048522542</v>
+        <v>0.356536502546689</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.538545296167247</v>
+        <v>0.502846299810247</v>
       </c>
       <c r="F4" t="n">
-        <v>0.13550135501355</v>
+        <v>0.165591397849462</v>
       </c>
       <c r="G4" t="n">
-        <v>0.58176434102323</v>
+        <v>0.329397611833898</v>
       </c>
       <c r="H4" t="n">
-        <v>0.157723577235772</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.380863039399625</v>
+        <v>0.365591397849462</v>
       </c>
       <c r="J4" t="n">
-        <v>0.352740624180435</v>
+        <v>0.193548387096774</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
-        <v>0.317857142857143</v>
+      <c r="B5" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="C5" t="n">
-        <v>0.505896424374685</v>
+        <v>0.325698813764329</v>
       </c>
       <c r="D5" t="n">
-        <v>0.538545296167247</v>
+        <v>0.502846299810247</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.368055555555556</v>
+        <v>0.363398692810458</v>
       </c>
       <c r="G5" t="n">
-        <v>0.522068733153639</v>
+        <v>0.548261293467663</v>
       </c>
       <c r="H5" t="n">
-        <v>0.410119047619048</v>
+        <v>0.0392156862745098</v>
       </c>
       <c r="I5" t="n">
-        <v>0.644917582417582</v>
+        <v>0.758169934640523</v>
       </c>
       <c r="J5" t="n">
-        <v>0.602630568356375</v>
+        <v>0.287581699346405</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
-        <v>0.585714285714286</v>
+      <c r="B6" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="C6" t="n">
-        <v>0.205966836401619</v>
+        <v>0.212676853423882</v>
       </c>
       <c r="D6" t="n">
-        <v>0.13550135501355</v>
+        <v>0.165591397849462</v>
       </c>
       <c r="E6" t="n">
-        <v>0.368055555555556</v>
+        <v>0.363398692810458</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.213654179199708</v>
+        <v>0.226887661141805</v>
       </c>
       <c r="H6" t="n">
-        <v>0.833333333333333</v>
+        <v>0.133333333333333</v>
       </c>
       <c r="I6" t="n">
-        <v>0.376068376068376</v>
+        <v>0.355555555555556</v>
       </c>
       <c r="J6" t="n">
-        <v>0.362007168458781</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
-        <v>0.179655455291222</v>
+      <c r="B7" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="C7" t="n">
-        <v>0.436445469259251</v>
+        <v>0.43985967413633</v>
       </c>
       <c r="D7" t="n">
-        <v>0.58176434102323</v>
+        <v>0.329397611833898</v>
       </c>
       <c r="E7" t="n">
-        <v>0.522068733153639</v>
+        <v>0.548261293467663</v>
       </c>
       <c r="F7" t="n">
-        <v>0.213654179199708</v>
+        <v>0.226887661141805</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.188679245283019</v>
+        <v>0.0151933701657459</v>
       </c>
       <c r="I7" t="n">
-        <v>0.460844323846785</v>
+        <v>0.437691835481891</v>
       </c>
       <c r="J7" t="n">
-        <v>0.535455644058677</v>
+        <v>0.229005524861878</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
-        <v>0.752380952380952</v>
+      <c r="B8" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="C8" t="n">
-        <v>0.266118292205249</v>
+        <v>0.0899830220713073</v>
       </c>
       <c r="D8" t="n">
-        <v>0.157723577235772</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.410119047619048</v>
+        <v>0.0392156862745098</v>
       </c>
       <c r="F8" t="n">
-        <v>0.833333333333333</v>
+        <v>0.133333333333333</v>
       </c>
       <c r="G8" t="n">
-        <v>0.188679245283019</v>
+        <v>0.0151933701657459</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.430769230769231</v>
+        <v>0.111111111111111</v>
       </c>
       <c r="J8" t="n">
-        <v>0.268100358422939</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
-        <v>0.23956043956044</v>
+      <c r="B9" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="C9" t="n">
-        <v>0.224984181505921</v>
+        <v>0.147707979626486</v>
       </c>
       <c r="D9" t="n">
-        <v>0.380863039399625</v>
+        <v>0.365591397849462</v>
       </c>
       <c r="E9" t="n">
-        <v>0.644917582417582</v>
+        <v>0.758169934640523</v>
       </c>
       <c r="F9" t="n">
-        <v>0.376068376068376</v>
+        <v>0.355555555555556</v>
       </c>
       <c r="G9" t="n">
-        <v>0.460844323846785</v>
+        <v>0.437691835481891</v>
       </c>
       <c r="H9" t="n">
-        <v>0.430769230769231</v>
+        <v>0.111111111111111</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.719465122690929</v>
+        <v>0.222222222222222</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
-        <v>0.123348694316436</v>
+      <c r="B10" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="C10" t="n">
-        <v>0.205825741590117</v>
+        <v>0.344312393887946</v>
       </c>
       <c r="D10" t="n">
-        <v>0.352740624180435</v>
+        <v>0.193548387096774</v>
       </c>
       <c r="E10" t="n">
-        <v>0.602630568356375</v>
+        <v>0.287581699346405</v>
       </c>
       <c r="F10" t="n">
-        <v>0.362007168458781</v>
+        <v>0.4</v>
       </c>
       <c r="G10" t="n">
-        <v>0.535455644058677</v>
+        <v>0.229005524861878</v>
       </c>
       <c r="H10" t="n">
-        <v>0.268100358422939</v>
+        <v>0.6</v>
       </c>
       <c r="I10" t="n">
-        <v>0.719465122690929</v>
+        <v>0.222222222222222</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1868,282 +3014,250 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.305243676876497</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.436067600671154</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.61472251841081</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.321076997072689</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.336113200766159</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.541101634245343</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.625840931292206</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.361177471465137</v>
-      </c>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
-        <v>0.305243676876497</v>
-      </c>
+      <c r="B3"/>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.68693656160231</v>
+        <v>0.639063786634672</v>
       </c>
       <c r="E3" t="n">
-        <v>0.580220361996111</v>
+        <v>0.337152627341444</v>
       </c>
       <c r="F3" t="n">
-        <v>0.137780801384886</v>
+        <v>0.0854576889692517</v>
       </c>
       <c r="G3" t="n">
-        <v>0.802545007283661</v>
+        <v>0.827837626790776</v>
       </c>
       <c r="H3" t="n">
-        <v>0.168339423485314</v>
+        <v>0.168441356506852</v>
       </c>
       <c r="I3" t="n">
-        <v>0.390099367141153</v>
+        <v>0.235816683550981</v>
       </c>
       <c r="J3" t="n">
-        <v>0.488732235516376</v>
+        <v>0.106420843601746</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
-        <v>0.436067600671154</v>
-      </c>
+      <c r="B4"/>
       <c r="C4" t="n">
-        <v>0.68693656160231</v>
+        <v>0.639063786634672</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.689771495220447</v>
+        <v>0.491470242914458</v>
       </c>
       <c r="F4" t="n">
-        <v>0.181644821366971</v>
+        <v>0.180606325447129</v>
       </c>
       <c r="G4" t="n">
-        <v>0.730640328276071</v>
+        <v>0.701421742829482</v>
       </c>
       <c r="H4" t="n">
-        <v>0.220076467739888</v>
+        <v>0.338254814382728</v>
       </c>
       <c r="I4" t="n">
-        <v>0.502400982512788</v>
+        <v>0.430656752135304</v>
       </c>
       <c r="J4" t="n">
-        <v>0.462475894450686</v>
+        <v>0.228199802873835</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
-        <v>0.61472251841081</v>
-      </c>
+      <c r="B5"/>
       <c r="C5" t="n">
-        <v>0.580220361996111</v>
+        <v>0.337152627341444</v>
       </c>
       <c r="D5" t="n">
-        <v>0.689771495220447</v>
+        <v>0.491470242914458</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.296695941127773</v>
+        <v>0.40551716153728</v>
       </c>
       <c r="G5" t="n">
-        <v>0.587895640617492</v>
+        <v>0.38565180518773</v>
       </c>
       <c r="H5" t="n">
-        <v>0.347903370993209</v>
+        <v>0.653229768050864</v>
       </c>
       <c r="I5" t="n">
-        <v>0.73757177029049</v>
+        <v>0.799669165791757</v>
       </c>
       <c r="J5" t="n">
-        <v>0.458707160663117</v>
+        <v>0.601010818341337</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
-        <v>0.321076997072689</v>
-      </c>
+      <c r="B6"/>
       <c r="C6" t="n">
-        <v>0.137780801384886</v>
+        <v>0.0854576889692517</v>
       </c>
       <c r="D6" t="n">
-        <v>0.181644821366971</v>
+        <v>0.180606325447129</v>
       </c>
       <c r="E6" t="n">
-        <v>0.296695941127773</v>
+        <v>0.40551716153728</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.133709311071753</v>
+        <v>0.0970622041375175</v>
       </c>
       <c r="H6" t="n">
-        <v>0.356605278793425</v>
+        <v>0.508004278288948</v>
       </c>
       <c r="I6" t="n">
-        <v>0.425689027258335</v>
+        <v>0.431997017236183</v>
       </c>
       <c r="J6" t="n">
-        <v>0.180356935107764</v>
+        <v>0.443751800533046</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
-        <v>0.336113200766159</v>
-      </c>
+      <c r="B7"/>
       <c r="C7" t="n">
-        <v>0.802545007283661</v>
+        <v>0.827837626790776</v>
       </c>
       <c r="D7" t="n">
-        <v>0.730640328276071</v>
+        <v>0.701421742829482</v>
       </c>
       <c r="E7" t="n">
-        <v>0.587895640617492</v>
+        <v>0.38565180518773</v>
       </c>
       <c r="F7" t="n">
-        <v>0.133709311071753</v>
+        <v>0.0970622041375175</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.166296628041595</v>
+        <v>0.181497949205913</v>
       </c>
       <c r="I7" t="n">
-        <v>0.411270572442309</v>
+        <v>0.32287215719326</v>
       </c>
       <c r="J7" t="n">
-        <v>0.475997909536245</v>
+        <v>0.118466250088898</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
-        <v>0.541101634245343</v>
-      </c>
+      <c r="B8"/>
       <c r="C8" t="n">
-        <v>0.168339423485314</v>
+        <v>0.168441356506852</v>
       </c>
       <c r="D8" t="n">
-        <v>0.220076467739888</v>
+        <v>0.338254814382728</v>
       </c>
       <c r="E8" t="n">
-        <v>0.347903370993209</v>
+        <v>0.653229768050864</v>
       </c>
       <c r="F8" t="n">
-        <v>0.356605278793425</v>
+        <v>0.508004278288948</v>
       </c>
       <c r="G8" t="n">
-        <v>0.166296628041595</v>
+        <v>0.181497949205913</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.406400214967509</v>
+        <v>0.690876296980737</v>
       </c>
       <c r="J8" t="n">
-        <v>0.251308068266612</v>
+        <v>0.724257456726442</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
-        <v>0.625840931292206</v>
-      </c>
+      <c r="B9"/>
       <c r="C9" t="n">
-        <v>0.390099367141153</v>
+        <v>0.235816683550981</v>
       </c>
       <c r="D9" t="n">
-        <v>0.502400982512788</v>
+        <v>0.430656752135304</v>
       </c>
       <c r="E9" t="n">
-        <v>0.73757177029049</v>
+        <v>0.799669165791757</v>
       </c>
       <c r="F9" t="n">
-        <v>0.425689027258335</v>
+        <v>0.431997017236183</v>
       </c>
       <c r="G9" t="n">
-        <v>0.411270572442309</v>
+        <v>0.32287215719326</v>
       </c>
       <c r="H9" t="n">
-        <v>0.406400214967509</v>
+        <v>0.690876296980737</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.329979236178828</v>
+        <v>0.612529190411972</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
-        <v>0.361177471465137</v>
-      </c>
+      <c r="B10"/>
       <c r="C10" t="n">
-        <v>0.488732235516376</v>
+        <v>0.106420843601746</v>
       </c>
       <c r="D10" t="n">
-        <v>0.462475894450686</v>
+        <v>0.228199802873835</v>
       </c>
       <c r="E10" t="n">
-        <v>0.458707160663117</v>
+        <v>0.601010818341337</v>
       </c>
       <c r="F10" t="n">
-        <v>0.180356935107764</v>
+        <v>0.443751800533046</v>
       </c>
       <c r="G10" t="n">
-        <v>0.475997909536245</v>
+        <v>0.118466250088898</v>
       </c>
       <c r="H10" t="n">
-        <v>0.251308068266612</v>
+        <v>0.724257456726442</v>
       </c>
       <c r="I10" t="n">
-        <v>0.329979236178828</v>
+        <v>0.612529190411972</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -2199,282 +3313,250 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.209520277873167</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.273537392219202</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.266006295901399</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.363310312237938</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.178850038472029</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.652681715697432</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.284782453127769</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.488025305994986</v>
-      </c>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
-        <v>0.209520277873167</v>
-      </c>
+      <c r="B3"/>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.812740661948913</v>
+        <v>0.735762906000645</v>
       </c>
       <c r="E3" t="n">
-        <v>0.724255513593499</v>
+        <v>0.628366280151764</v>
       </c>
       <c r="F3" t="n">
-        <v>0.660268419222831</v>
+        <v>0.709637700791046</v>
       </c>
       <c r="G3" t="n">
-        <v>0.787012171141441</v>
+        <v>0.779592806713899</v>
       </c>
       <c r="H3" t="n">
-        <v>0.155639309867282</v>
+        <v>0.398995634497629</v>
       </c>
       <c r="I3" t="n">
-        <v>0.476824214715987</v>
+        <v>0.534481719868058</v>
       </c>
       <c r="J3" t="n">
-        <v>0.252812860398708</v>
+        <v>0.34807990139193</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
-        <v>0.273537392219202</v>
-      </c>
+      <c r="B4"/>
       <c r="C4" t="n">
-        <v>0.812740661948913</v>
+        <v>0.735762906000645</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.682081537734085</v>
+        <v>0.60344996206943</v>
       </c>
       <c r="F4" t="n">
-        <v>0.786452787437038</v>
+        <v>0.851335691389517</v>
       </c>
       <c r="G4" t="n">
-        <v>0.776504085361446</v>
+        <v>0.809571773969764</v>
       </c>
       <c r="H4" t="n">
-        <v>0.137651729356338</v>
+        <v>0.342554772713478</v>
       </c>
       <c r="I4" t="n">
-        <v>0.446863869537631</v>
+        <v>0.455631540600078</v>
       </c>
       <c r="J4" t="n">
-        <v>0.248020415371697</v>
+        <v>0.249835152003645</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
-        <v>0.266006295901399</v>
-      </c>
+      <c r="B5"/>
       <c r="C5" t="n">
-        <v>0.724255513593499</v>
+        <v>0.628366280151764</v>
       </c>
       <c r="D5" t="n">
-        <v>0.682081537734085</v>
+        <v>0.60344996206943</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.60532935806155</v>
+        <v>0.628552131813867</v>
       </c>
       <c r="G5" t="n">
-        <v>0.749050147469219</v>
+        <v>0.636900159834434</v>
       </c>
       <c r="H5" t="n">
-        <v>0.147421353611911</v>
+        <v>0.254470342408185</v>
       </c>
       <c r="I5" t="n">
-        <v>0.617245902561607</v>
+        <v>0.805817688795053</v>
       </c>
       <c r="J5" t="n">
-        <v>0.341323354013336</v>
+        <v>0.171192779689238</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
-        <v>0.363310312237938</v>
-      </c>
+      <c r="B6"/>
       <c r="C6" t="n">
-        <v>0.660268419222831</v>
+        <v>0.709637700791046</v>
       </c>
       <c r="D6" t="n">
-        <v>0.786452787437038</v>
+        <v>0.851335691389517</v>
       </c>
       <c r="E6" t="n">
-        <v>0.60532935806155</v>
+        <v>0.628552131813867</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.579072382636612</v>
+        <v>0.689615794938157</v>
       </c>
       <c r="H6" t="n">
-        <v>0.20509042822007</v>
+        <v>0.410918344449103</v>
       </c>
       <c r="I6" t="n">
-        <v>0.50600015091996</v>
+        <v>0.471930683944199</v>
       </c>
       <c r="J6" t="n">
-        <v>0.355739290125869</v>
+        <v>0.311839109925163</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
-        <v>0.178850038472029</v>
-      </c>
+      <c r="B7"/>
       <c r="C7" t="n">
-        <v>0.787012171141441</v>
+        <v>0.779592806713899</v>
       </c>
       <c r="D7" t="n">
-        <v>0.776504085361446</v>
+        <v>0.809571773969764</v>
       </c>
       <c r="E7" t="n">
-        <v>0.749050147469219</v>
+        <v>0.636900159834434</v>
       </c>
       <c r="F7" t="n">
-        <v>0.579072382636612</v>
+        <v>0.689615794938157</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0878406981104753</v>
+        <v>0.285104859590992</v>
       </c>
       <c r="I7" t="n">
-        <v>0.395756504185983</v>
+        <v>0.492622244028102</v>
       </c>
       <c r="J7" t="n">
-        <v>0.168492590505579</v>
+        <v>0.220152090788619</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
-        <v>0.652681715697432</v>
-      </c>
+      <c r="B8"/>
       <c r="C8" t="n">
-        <v>0.155639309867282</v>
+        <v>0.398995634497629</v>
       </c>
       <c r="D8" t="n">
-        <v>0.137651729356338</v>
+        <v>0.342554772713478</v>
       </c>
       <c r="E8" t="n">
-        <v>0.147421353611911</v>
+        <v>0.254470342408185</v>
       </c>
       <c r="F8" t="n">
-        <v>0.20509042822007</v>
+        <v>0.410918344449103</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0878406981104753</v>
+        <v>0.285104859590992</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.197090018198834</v>
+        <v>0.228547846531879</v>
       </c>
       <c r="J8" t="n">
-        <v>0.465805769456769</v>
+        <v>0.327314888397638</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
-        <v>0.284782453127769</v>
-      </c>
+      <c r="B9"/>
       <c r="C9" t="n">
-        <v>0.476824214715987</v>
+        <v>0.534481719868058</v>
       </c>
       <c r="D9" t="n">
-        <v>0.446863869537631</v>
+        <v>0.455631540600078</v>
       </c>
       <c r="E9" t="n">
-        <v>0.617245902561607</v>
+        <v>0.805817688795053</v>
       </c>
       <c r="F9" t="n">
-        <v>0.50600015091996</v>
+        <v>0.471930683944199</v>
       </c>
       <c r="G9" t="n">
-        <v>0.395756504185983</v>
+        <v>0.492622244028102</v>
       </c>
       <c r="H9" t="n">
-        <v>0.197090018198834</v>
+        <v>0.228547846531879</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.542438695909879</v>
+        <v>0.117051592209818</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
-        <v>0.488025305994986</v>
-      </c>
+      <c r="B10"/>
       <c r="C10" t="n">
-        <v>0.252812860398708</v>
+        <v>0.34807990139193</v>
       </c>
       <c r="D10" t="n">
-        <v>0.248020415371697</v>
+        <v>0.249835152003645</v>
       </c>
       <c r="E10" t="n">
-        <v>0.341323354013336</v>
+        <v>0.171192779689238</v>
       </c>
       <c r="F10" t="n">
-        <v>0.355739290125869</v>
+        <v>0.311839109925163</v>
       </c>
       <c r="G10" t="n">
-        <v>0.168492590505579</v>
+        <v>0.220152090788619</v>
       </c>
       <c r="H10" t="n">
-        <v>0.465805769456769</v>
+        <v>0.327314888397638</v>
       </c>
       <c r="I10" t="n">
-        <v>0.542438695909879</v>
+        <v>0.117051592209818</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -2530,282 +3612,250 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.117</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B3"/>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.015</v>
+        <v>0.508928739074127</v>
       </c>
       <c r="E3" t="n">
-        <v>0.075</v>
+        <v>0.656286627135303</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.349163175125387</v>
       </c>
       <c r="G3" t="n">
-        <v>0.025</v>
+        <v>0.729772866391214</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.403286188766509</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006</v>
+        <v>0.509971163025831</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.108063944201569</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
+      <c r="B4"/>
       <c r="C4" t="n">
-        <v>0.015</v>
+        <v>0.508928739074127</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.149</v>
+        <v>0.714029133938419</v>
       </c>
       <c r="F4" t="n">
-        <v>0.337</v>
+        <v>0.549915490181797</v>
       </c>
       <c r="G4" t="n">
-        <v>0.111</v>
+        <v>0.720368119405164</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.603360812174254</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004</v>
+        <v>0.519363390747638</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>0.212968879333745</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
+      <c r="B5"/>
       <c r="C5" t="n">
-        <v>0.075</v>
+        <v>0.656286627135303</v>
       </c>
       <c r="D5" t="n">
-        <v>0.149</v>
+        <v>0.714029133938419</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001</v>
+        <v>0.446425972533362</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004</v>
+        <v>0.705594724565848</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.544786476881393</v>
       </c>
       <c r="I5" t="n">
-        <v>0.049</v>
+        <v>0.673810669464747</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.12632213564987</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B6"/>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.349163175125387</v>
       </c>
       <c r="D6" t="n">
-        <v>0.337</v>
+        <v>0.549915490181797</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001</v>
+        <v>0.446425972533362</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001</v>
+        <v>0.486419400301284</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.348623036212941</v>
       </c>
       <c r="I6" t="n">
-        <v>0.039</v>
+        <v>0.409546649694133</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.476751458665529</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
+      <c r="B7"/>
       <c r="C7" t="n">
-        <v>0.025</v>
+        <v>0.729772866391214</v>
       </c>
       <c r="D7" t="n">
-        <v>0.111</v>
+        <v>0.720368119405164</v>
       </c>
       <c r="E7" t="n">
-        <v>0.004</v>
+        <v>0.705594724565848</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001</v>
+        <v>0.486419400301284</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.524849746376366</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001</v>
+        <v>0.530096855220695</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.165663583752696</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
-        <v>0.117</v>
-      </c>
+      <c r="B8"/>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.403286188766509</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.603360812174254</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.544786476881393</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.348623036212941</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.524849746376366</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.062</v>
+        <v>0.325958182948837</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.105530681389017</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
-        <v>0.103</v>
-      </c>
+      <c r="B9"/>
       <c r="C9" t="n">
-        <v>0.006</v>
+        <v>0.509971163025831</v>
       </c>
       <c r="D9" t="n">
-        <v>0.004</v>
+        <v>0.519363390747638</v>
       </c>
       <c r="E9" t="n">
-        <v>0.049</v>
+        <v>0.673810669464747</v>
       </c>
       <c r="F9" t="n">
-        <v>0.039</v>
+        <v>0.409546649694133</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001</v>
+        <v>0.530096855220695</v>
       </c>
       <c r="H9" t="n">
-        <v>0.062</v>
+        <v>0.325958182948837</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.0765938241519303</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
+      <c r="B10"/>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.108063944201569</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>0.212968879333745</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.12632213564987</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.476751458665529</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.165663583752696</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.105530681389017</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.0765938241519303</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -2861,282 +3911,250 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.069</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.706</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B3"/>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.454168970304735</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.670759890805713</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.336523435773101</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.741145023581824</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.289663833347553</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.600279844784435</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.479642391745418</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
+      <c r="B4"/>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>0.454168970304735</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.408157890651356</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.517840911640434</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.396765621624257</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.116380922630196</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001</v>
+        <v>0.446823206767827</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>0.360726078311353</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
+      <c r="B5"/>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.670759890805713</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.408157890651356</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.469564636045485</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.6002407200632</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.360273808346406</v>
       </c>
       <c r="I5" t="n">
-        <v>0.211</v>
+        <v>0.793867063081376</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.473176132512671</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
-        <v>0.069</v>
-      </c>
+      <c r="B6"/>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.336523435773101</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.517840911640434</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.469564636045485</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.26658337151818</v>
       </c>
       <c r="H6" t="n">
-        <v>0.975</v>
+        <v>0.185025810868374</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007</v>
+        <v>0.505173902076629</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.469607187423937</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
+      <c r="B7"/>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>0.741145023581824</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.396765621624257</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.6002407200632</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.26658337151818</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.231094569964714</v>
       </c>
       <c r="I7" t="n">
-        <v>0.003</v>
+        <v>0.591927111297875</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.388040558048945</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
-        <v>0.706</v>
-      </c>
+      <c r="B8"/>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.289663833347553</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.116380922630196</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.360273808346406</v>
       </c>
       <c r="F8" t="n">
-        <v>0.975</v>
+        <v>0.185025810868374</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.231094569964714</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.044</v>
+        <v>0.250832011634135</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.148584211387578</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
+      <c r="B9"/>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.600279844784435</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001</v>
+        <v>0.446823206767827</v>
       </c>
       <c r="E9" t="n">
-        <v>0.211</v>
+        <v>0.793867063081376</v>
       </c>
       <c r="F9" t="n">
-        <v>0.007</v>
+        <v>0.505173902076629</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003</v>
+        <v>0.591927111297875</v>
       </c>
       <c r="H9" t="n">
-        <v>0.044</v>
+        <v>0.250832011634135</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.475</v>
+        <v>0.457154930063075</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
+      <c r="B10"/>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.479642391745418</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>0.360726078311353</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.473176132512671</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.469607187423937</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.388040558048945</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.148584211387578</v>
       </c>
       <c r="I10" t="n">
-        <v>0.475</v>
+        <v>0.457154930063075</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -3192,38 +4210,20 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B3"/>
       <c r="C3" t="n">
         <v>1</v>
       </c>
@@ -3234,28 +4234,26 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.556</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.765</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
+      <c r="B4"/>
       <c r="C4" t="n">
         <v>0.002</v>
       </c>
@@ -3263,115 +4261,109 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001</v>
+        <v>0.054</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.241</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009</v>
+        <v>0.162</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.224</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008</v>
+        <v>0.205</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
+      <c r="B5"/>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001</v>
+        <v>0.054</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.562</v>
       </c>
       <c r="I5" t="n">
-        <v>0.199</v>
+        <v>0.821</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B6"/>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.241</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.504</v>
       </c>
       <c r="I6" t="n">
-        <v>0.004</v>
+        <v>0.03</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
+      <c r="B7"/>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009</v>
+        <v>0.162</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.613</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -3381,93 +4373,87 @@
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
+      <c r="B8"/>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.556</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.224</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.562</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.504</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.004</v>
+        <v>0.314</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.682</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
-        <v>0.042</v>
-      </c>
+      <c r="B9"/>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.765</v>
       </c>
       <c r="D9" t="n">
-        <v>0.008</v>
+        <v>0.205</v>
       </c>
       <c r="E9" t="n">
-        <v>0.199</v>
+        <v>0.821</v>
       </c>
       <c r="F9" t="n">
-        <v>0.004</v>
+        <v>0.03</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.613</v>
       </c>
       <c r="H9" t="n">
-        <v>0.004</v>
+        <v>0.314</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
+      <c r="B10"/>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.682</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -3523,55 +4509,37 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B3"/>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -3584,11 +4552,9 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
+      <c r="B4"/>
       <c r="C4" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -3597,16 +4563,16 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.212</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -3616,9 +4582,7 @@
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
+      <c r="B5"/>
       <c r="C5" t="n">
         <v>0</v>
       </c>
@@ -3638,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.013</v>
+        <v>0.778</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -3648,14 +4612,12 @@
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B6"/>
       <c r="C6" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.212</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3667,27 +4629,25 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008</v>
+        <v>0.012</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
+      <c r="B7"/>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3702,7 +4662,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -3712,11 +4672,9 @@
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
-        <v>0.035</v>
-      </c>
+      <c r="B8"/>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -3725,7 +4683,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -3734,51 +4692,47 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.793</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
+      <c r="B9"/>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="E9" t="n">
-        <v>0.013</v>
+        <v>0.778</v>
       </c>
       <c r="F9" t="n">
-        <v>0.008</v>
+        <v>0.012</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
+      <c r="B10"/>
       <c r="C10" t="n">
         <v>0</v>
       </c>
@@ -3789,16 +4743,16 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.793</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -3854,282 +4808,250 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.230389063977448</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.262460935138316</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.356658462085148</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.376333515097093</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.223398960270309</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.619893229409181</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.42745670533391</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.274631006307131</v>
-      </c>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
-        <v>0.230389063977448</v>
-      </c>
+      <c r="B3"/>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.612879681731421</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.636155304381705</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3550214625887</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.687513951099019</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.197244950731546</v>
+        <v>0.103</v>
       </c>
       <c r="I3" t="n">
-        <v>0.381888501833832</v>
+        <v>0.001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.265128549670019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
-        <v>0.262460935138316</v>
-      </c>
+      <c r="B4"/>
       <c r="C4" t="n">
-        <v>0.612879681731421</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.656804522527196</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.444460257470594</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.703126559360283</v>
+        <v>0.015</v>
       </c>
       <c r="H4" t="n">
-        <v>0.16508275001528</v>
+        <v>0.207</v>
       </c>
       <c r="I4" t="n">
-        <v>0.439395055225364</v>
+        <v>0.024</v>
       </c>
       <c r="J4" t="n">
-        <v>0.275113499262004</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
-        <v>0.356658462085148</v>
-      </c>
+      <c r="B5"/>
       <c r="C5" t="n">
-        <v>0.636155304381705</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.656804522527196</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.428542510721871</v>
+        <v>0.002</v>
       </c>
       <c r="G5" t="n">
-        <v>0.642409660037856</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.289344472199737</v>
+        <v>0.586</v>
       </c>
       <c r="I5" t="n">
-        <v>0.627947006467048</v>
+        <v>0.821</v>
       </c>
       <c r="J5" t="n">
-        <v>0.366322365537179</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
-        <v>0.376333515097093</v>
-      </c>
+      <c r="B6"/>
       <c r="C6" t="n">
-        <v>0.3550214625887</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.444460257470594</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.428542510721871</v>
+        <v>0.002</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.337746969164665</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.416118819981451</v>
+        <v>0.373</v>
       </c>
       <c r="I6" t="n">
-        <v>0.44231487499991</v>
+        <v>0.036</v>
       </c>
       <c r="J6" t="n">
-        <v>0.269802534949764</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
-        <v>0.223398960270309</v>
-      </c>
+      <c r="B7"/>
       <c r="C7" t="n">
-        <v>0.687513951099019</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.703126559360283</v>
+        <v>0.015</v>
       </c>
       <c r="E7" t="n">
-        <v>0.642409660037856</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.337746969164665</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.144778092764955</v>
+        <v>0.108</v>
       </c>
       <c r="I7" t="n">
-        <v>0.42714106625329</v>
+        <v>0.003</v>
       </c>
       <c r="J7" t="n">
-        <v>0.301238373303654</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
-        <v>0.619893229409181</v>
-      </c>
+      <c r="B8"/>
       <c r="C8" t="n">
-        <v>0.197244950731546</v>
+        <v>0.103</v>
       </c>
       <c r="D8" t="n">
-        <v>0.16508275001528</v>
+        <v>0.207</v>
       </c>
       <c r="E8" t="n">
-        <v>0.289344472199737</v>
+        <v>0.586</v>
       </c>
       <c r="F8" t="n">
-        <v>0.416118819981451</v>
+        <v>0.373</v>
       </c>
       <c r="G8" t="n">
-        <v>0.144778092764955</v>
+        <v>0.108</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.371001141575887</v>
+        <v>0.706</v>
       </c>
       <c r="J8" t="n">
-        <v>0.324133921470519</v>
+        <v>0.708</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
-        <v>0.42745670533391</v>
-      </c>
+      <c r="B9"/>
       <c r="C9" t="n">
-        <v>0.381888501833832</v>
+        <v>0.001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.439395055225364</v>
+        <v>0.024</v>
       </c>
       <c r="E9" t="n">
-        <v>0.627947006467048</v>
+        <v>0.821</v>
       </c>
       <c r="F9" t="n">
-        <v>0.44231487499991</v>
+        <v>0.036</v>
       </c>
       <c r="G9" t="n">
-        <v>0.42714106625329</v>
+        <v>0.003</v>
       </c>
       <c r="H9" t="n">
-        <v>0.371001141575887</v>
+        <v>0.706</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.427272919144612</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
-        <v>0.274631006307131</v>
-      </c>
+      <c r="B10"/>
       <c r="C10" t="n">
-        <v>0.265128549670019</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.275113499262004</v>
+        <v>0.002</v>
       </c>
       <c r="E10" t="n">
-        <v>0.366322365537179</v>
+        <v>0.047</v>
       </c>
       <c r="F10" t="n">
-        <v>0.269802534949764</v>
+        <v>0.028</v>
       </c>
       <c r="G10" t="n">
-        <v>0.301238373303654</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.324133921470519</v>
+        <v>0.708</v>
       </c>
       <c r="I10" t="n">
-        <v>0.427272919144612</v>
+        <v>0.26</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
